--- a/imports/templates/costs.xlsx
+++ b/imports/templates/costs.xlsx
@@ -756,7 +756,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Optional. Reference exchange rate. NUMERIC(10,4). Never used for conversion.</t>
+          <t>Required. PEN per USD rate at transaction date. NUMERIC(10,4).</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">

--- a/imports/templates/costs.xlsx
+++ b/imports/templates/costs.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -483,20 +483,19 @@
     <col width="44" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="44" customWidth="1" min="9" max="9"/>
     <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
-    <col width="35" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
     <col width="44" customWidth="1" min="13" max="13"/>
-    <col width="44" customWidth="1" min="14" max="14"/>
-    <col width="38" customWidth="1" min="15" max="15"/>
-    <col width="39" customWidth="1" min="16" max="16"/>
+    <col width="38" customWidth="1" min="14" max="14"/>
+    <col width="39" customWidth="1" min="15" max="15"/>
+    <col width="44" customWidth="1" min="16" max="16"/>
     <col width="44" customWidth="1" min="17" max="17"/>
     <col width="44" customWidth="1" min="18" max="18"/>
-    <col width="44" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,90 +506,85 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>valuation_number</t>
+          <t>bank_name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>bank_name</t>
+          <t>bank_account_last4</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>bank_account_last4</t>
+          <t>entity_document_number</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>entity_document_number</t>
+          <t>quote_document_ref</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>quote_document_ref</t>
+          <t>cost_type</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>cost_type</t>
+          <t>date</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>igv_rate</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>igv_rate</t>
+          <t>detraccion_rate</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>detraccion_rate</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>exchange_rate</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>exchange_rate</t>
+          <t>comprobante_type</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>comprobante_type</t>
+          <t>comprobante_number</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>comprobante_number</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>document_ref</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>document_ref</t>
+          <t>due_date</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>due_date</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -604,90 +598,85 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BCP</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>BCP</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>20612345678</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>20612345678</t>
+          <t>PRY001-QT-001</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>PRY001-QT-001</t>
+          <t>project_cost</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>project_cost</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>Cement purchase for foundation work</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Cement purchase for foundation work</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>PEN</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>PEN</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>factura</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>factura</t>
+          <t>F001-00234</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>F001-00234</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>bank_transfer</t>
+          <t>PRY001-AP-001</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>PRY001-AP-001</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Urgent delivery requested</t>
         </is>
@@ -701,90 +690,85 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Optional. Valuation number within the project. Requires project_code.</t>
+          <t>Required. Bank name. Used with bank_account_last4 to resolve bank account.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Required. Bank name. Used with bank_account_last4 to resolve bank account.</t>
+          <t>Required. Last 4 digits of bank account. Used with bank_name to resolve bank account.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Required. Last 4 digits of bank account. Used with bank_name to resolve bank account.</t>
+          <t>Optional. Supplier/vendor document number. Null if informal/unassigned.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Optional. Supplier/vendor document number. Null if informal/unassigned.</t>
+          <t>Optional. Document ref of a prior accepted quote. Null if no prior quote.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Optional. Document ref of a prior accepted quote. Null if no prior quote.</t>
+          <t>Required. Type of cost.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Required. Type of cost.</t>
+          <t>Required. Date the expense occurred. Format: YYYY-MM-DD.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Required. Date the expense occurred. Format: YYYY-MM-DD.</t>
+          <t>Required. Overall invoice or expense title.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Required. Overall invoice or expense title.</t>
+          <t>Required. IGV percentage. NUMERIC(5,2). Default 18.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Required. IGV percentage. NUMERIC(5,2). Default 18.</t>
+          <t>Optional. Detracción percentage. NUMERIC(5,2). Null if not applicable.</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Optional. Detracción percentage. NUMERIC(5,2). Null if not applicable.</t>
+          <t>Required. Currency of the cost.</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Required. Currency of the cost.</t>
+          <t>Required. PEN per USD rate at transaction date. NUMERIC(10,4).</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Required. PEN per USD rate at transaction date. NUMERIC(10,4).</t>
+          <t>Optional. Type of payment document.</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Optional. Type of payment document.</t>
+          <t>Optional. Payment document number.</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>Optional. Payment document number.</t>
+          <t>Optional. How the payment was made.</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Optional. How the payment was made.</t>
+          <t>Optional. Document reference linking to SharePoint PDF.</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>Optional. Document reference linking to SharePoint PDF.</t>
+          <t>Optional. Payment due date. Feeds AP payment calendar. Format: YYYY-MM-DD.</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>Optional. Payment due date. Feeds AP payment calendar. Format: YYYY-MM-DD.</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>Optional. Free-form context about the cost.</t>
         </is>
@@ -798,66 +782,61 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Lookup → valuations (by project + number)</t>
+          <t>Lookup → bank_accounts.bank_name</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Lookup → bank_accounts.bank_name</t>
+          <t>Lookup → bank_accounts.account_number_last4</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Lookup → bank_accounts.account_number_last4</t>
+          <t>Lookup → entities.document_number</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Lookup → entities.document_number</t>
+          <t>Lookup → quotes.document_ref</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Lookup → quotes.document_ref</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
           <t>project_cost | sga</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Usually 18</t>
+        </is>
+      </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Usually 18</t>
+          <t>Varies by service type</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Varies by service type</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
           <t>USD | PEN</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>factura | boleta | recibo_por_honorarios | liquidacion_de_compra | planilla_jornales | none</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>bank_transfer | cash | check</t>
         </is>
       </c>
+      <c r="P4" s="4" t="inlineStr"/>
       <c r="Q4" s="4" t="inlineStr"/>
       <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/imports/templates/costs.xlsx
+++ b/imports/templates/costs.xlsx
@@ -475,368 +475,432 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="44" customWidth="1" min="9" max="9"/>
     <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="11" max="11"/>
     <col width="44" customWidth="1" min="12" max="12"/>
-    <col width="44" customWidth="1" min="13" max="13"/>
-    <col width="38" customWidth="1" min="14" max="14"/>
-    <col width="39" customWidth="1" min="15" max="15"/>
+    <col width="39" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
     <col width="44" customWidth="1" min="16" max="16"/>
-    <col width="44" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="17" max="17"/>
     <col width="44" customWidth="1" min="18" max="18"/>
+    <col width="44" customWidth="1" min="19" max="19"/>
+    <col width="44" customWidth="1" min="20" max="20"/>
+    <col width="44" customWidth="1" min="21" max="21"/>
+    <col width="44" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>document_ref</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>bank_account</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>igv_rate</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>project_code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>bank_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>bank_account_last4</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>entity_document_number</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_rate</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>comprobante_type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>comprobante_number</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>detraccion_rate</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>payment_method</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>quote_document_ref</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>cost_type</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>igv_rate</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>detraccion_rate</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>exchange_rate</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>comprobante_type</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>comprobante_number</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>due_date</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>document_ref</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>due_date</t>
+          <t>item_title</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>subtotal</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>unit_of_measure</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>unit_price</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>PRY001-AP-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Cement purchase for foundation work</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>BCP-4567</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>PRY001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>BCP</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>4567</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>20612345678</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>factura</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>F001-00234</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>bank_transfer</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>PRY001-QT-001</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>project_cost</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Cement purchase for foundation work</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>factura</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>F001-00234</t>
-        </is>
-      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>bank_transfer</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>PRY001-AP-001</t>
+          <t>Urgent delivery requested</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>Portland cement Type I x 42.5kg</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Urgent delivery requested</t>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>14250.00</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>bags</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>28.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Optional. Project code. Null if SG&amp;A. Must exist in projects table.</t>
+          <t>Required. Grouping key — rows with same value form one cost with multiple items.</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Required. Bank name. Used with bank_account_last4 to resolve bank account.</t>
+          <t>Required. Date the expense occurred. Format: YYYY-MM-DD.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Required. Last 4 digits of bank account. Used with bank_name to resolve bank account.</t>
+          <t>Required. Overall invoice or expense title.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>Required. Bank account label. Must exist in bank_accounts table.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Required. Currency of the cost.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Required. IGV percentage. NUMERIC(5,2). Default 18.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Optional. Project code. Blank = SG&amp;A. Derives cost_type automatically.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>Optional. Supplier/vendor document number. Null if informal/unassigned.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Optional. PEN per USD rate. Auto-looked up from exchange_rates table by date if blank.</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Optional. Type of payment document.</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Optional. Payment document number.</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Optional. Detracción percentage. NUMERIC(5,2). Null if not applicable.</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Optional. How the payment was made.</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Optional. Document ref of a prior accepted quote. Null if no prior quote.</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Required. Type of cost.</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Required. Date the expense occurred. Format: YYYY-MM-DD.</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Required. Overall invoice or expense title.</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Required. IGV percentage. NUMERIC(5,2). Default 18.</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Optional. Detracción percentage. NUMERIC(5,2). Null if not applicable.</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Required. Currency of the cost.</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Required. PEN per USD rate at transaction date. NUMERIC(10,4).</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Optional. Type of payment document.</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>Optional. Payment document number.</t>
-        </is>
-      </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>Optional. How the payment was made.</t>
+          <t>Optional. Payment due date. Feeds AP payment calendar. Format: YYYY-MM-DD.</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Optional. Document reference linking to SharePoint PDF.</t>
+          <t>Optional. Free-form context about the cost.</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>Optional. Payment due date. Feeds AP payment calendar. Format: YYYY-MM-DD.</t>
+          <t>Required. Line item title.</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>Optional. Free-form context about the cost.</t>
+          <t>Required. Cost category. Different allowed values for project costs vs SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>Required. NUMERIC(15,2). Line item total amount.</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Optional. NUMERIC(15,4). Null for lump sum lines.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>Optional. meters, units, hours, kg, days, bags, etc.</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Optional. NUMERIC(15,4). Null for lump sum lines.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Lookup → bank_accounts.label</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>USD | PEN</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Usually 18</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Lookup → projects.project_code</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Lookup → bank_accounts.bank_name</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Lookup → bank_accounts.account_number_last4</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Lookup → entities.document_number</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>factura | boleta | recibo_por_honorarios | liquidacion_de_compra | planilla_jornales | none</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Varies by service type</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>bank_transfer | cash | check</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Lookup → quotes.document_ref</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>project_cost | sga</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Usually 18</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Varies by service type</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>USD | PEN</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>factura | boleta | recibo_por_honorarios | liquidacion_de_compra | planilla_jornales | none</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>bank_transfer | cash | check</t>
-        </is>
-      </c>
+      <c r="O4" s="4" t="inlineStr"/>
       <c r="P4" s="4" t="inlineStr"/>
       <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>materials | labor | subcontractor | equipment_rental | permits_regulatory | software_licenses | partner_compensation | business_development | professional_services | office_admin | other</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
